--- a/Result/profitability/6757.xlsx
+++ b/Result/profitability/6757.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM29"/>
+  <dimension ref="A1:AM30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4113,6 +4113,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>6757</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4787</v>
+      </c>
+      <c r="D30" t="n">
+        <v>4014</v>
+      </c>
+      <c r="E30" t="n">
+        <v>773</v>
+      </c>
+      <c r="F30" t="n">
+        <v>16.15</v>
+      </c>
+      <c r="G30" t="n">
+        <v>428</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>8.94%</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>431</v>
+      </c>
+      <c r="K30" t="n">
+        <v>343</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M30" t="n">
+        <v>1.47375</v>
+      </c>
+      <c r="N30" t="n">
+        <v>28.30375</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
+      </c>
+      <c r="V30" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W30" t="n">
+        <v>-2.16</v>
+      </c>
+      <c r="X30" t="n">
+        <v>-0.7422680412371134</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>-24.53</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-0.6029990167158309</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>-0.3801652892561983</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>-8.82</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>-0.3532238686423709</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK30" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
